--- a/R_阿克苏_人员名单.xlsx
+++ b/R_阿克苏_人员名单.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9575"/>
+    <workbookView windowHeight="18180"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
   <si>
     <t>部门</t>
   </si>
@@ -43,19 +43,34 @@
     <t>管理者代表</t>
   </si>
   <si>
+    <t>任鸿</t>
+  </si>
+  <si>
     <t>运维部</t>
   </si>
   <si>
     <t>经理</t>
   </si>
   <si>
+    <t>黄玥玥</t>
+  </si>
+  <si>
     <t>研发部</t>
   </si>
   <si>
+    <t>牛硕</t>
+  </si>
+  <si>
     <t>人力部</t>
   </si>
   <si>
+    <t>钟晶晶</t>
+  </si>
+  <si>
     <t>质量部</t>
+  </si>
+  <si>
+    <t>王孝依</t>
   </si>
 </sst>
 </file>
@@ -1061,14 +1076,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="34.5555555555556" customWidth="1"/>
-    <col min="2" max="2" width="18.8888888888889" customWidth="1"/>
+    <col min="1" max="1" width="34.5583333333333" customWidth="1"/>
+    <col min="2" max="2" width="18.8916666666667" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.6" spans="1:3">
+    <row r="1" ht="15.75" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1079,48 +1094,58 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" ht="15.6" spans="1:3">
+    <row r="2" ht="15" spans="1:3">
       <c r="A2" s="2"/>
       <c r="B2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="3"/>
+      <c r="C2" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="3" ht="15.6" spans="1:3">
+    <row r="3" ht="15" spans="1:3">
       <c r="A3" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="6"/>
+        <v>6</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="4" ht="15.6" spans="1:3">
+    <row r="4" ht="15" spans="1:3">
       <c r="A4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="6"/>
+      <c r="C4" s="6" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="5" ht="15.6" spans="1:3">
+    <row r="5" ht="15" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="6"/>
+        <v>6</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="6" ht="15.6" spans="1:3">
+    <row r="6" ht="15" spans="1:3">
       <c r="A6" s="7" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="3"/>
+        <v>6</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>13</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1133,7 +1158,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1145,7 +1170,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
